--- a/output/parana/11_orcamento_mensal_completo.xlsx
+++ b/output/parana/11_orcamento_mensal_completo.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,42 +433,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>mes_ano</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ano_mes_str</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>receita_orcada</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>custo_orcado</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>margem_orcada</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>margem_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>mes_nome</t>
         </is>
@@ -468,7 +480,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,7 +512,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -532,7 +544,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -564,7 +576,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -596,7 +608,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -628,7 +640,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -660,7 +672,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,7 +704,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -724,7 +736,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -756,7 +768,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -788,7 +800,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -820,7 +832,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -852,7 +864,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -884,7 +896,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -916,7 +928,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -948,7 +960,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -980,7 +992,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1012,7 +1024,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1044,7 +1056,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1076,7 +1088,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1108,7 +1120,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1140,7 +1152,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1172,7 +1184,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1204,7 +1216,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C25" t="inlineStr">
